--- a/data/credit_bond_all_2026-10-19.xlsx
+++ b/data/credit_bond_all_2026-10-19.xlsx
@@ -940,15 +940,19 @@
         <v>5.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>33.78</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -1005,7 +1009,7 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>5.08</v>
+        <v>5.075</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
@@ -1170,15 +1174,19 @@
         <v>5.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>48.26</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.71</t>
@@ -1869,14 +1877,20 @@
       <c r="E8" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>42.3</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -2101,14 +2115,20 @@
       <c r="E9" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>27.84</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -2341,8 +2361,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>47.26</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -2575,8 +2599,12 @@
           <t>1.30 ~ 1.90</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>18.94</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -2807,8 +2835,12 @@
           <t>1.39 ~ 1.59</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>23.78</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -3039,8 +3071,12 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3267,8 +3303,12 @@
           <t>1.46 ~ 1.66</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>39.26</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1.59</t>
@@ -3324,7 +3364,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>0.68</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -3497,8 +3539,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>46.3</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>1.87</t>
@@ -3721,7 +3767,9 @@
       <c r="E16" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1.24 ~ 1.44</t>
@@ -3947,7 +3995,9 @@
       <c r="E17" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.07</t>
@@ -4177,14 +4227,20 @@
       <c r="E18" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.74</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>47.26</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -4240,7 +4296,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>1.18</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4407,8 +4465,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>40.26</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -4637,8 +4699,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>55.3</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -4863,8 +4929,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>52.3</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -5089,8 +5159,12 @@
           <t>1.60 ~ 1.98</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>47.78</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.81</t>
@@ -5832,7 +5906,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -6976,7 +7052,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>2.74</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -7204,7 +7282,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>3.36</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
@@ -7664,7 +7744,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>6.03</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
@@ -7900,7 +7982,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>6.08</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
@@ -8828,7 +8912,9 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>4.3</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
@@ -9060,7 +9146,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>2.35</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
@@ -9296,7 +9384,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U40" s="3"/>
+      <c r="U40" s="4" t="n">
+        <v>5.73</v>
+      </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -9758,7 +9848,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4" t="n">
+        <v>5.94</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
@@ -10358,7 +10450,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26建行二级资本债03B(BC)</t>
+          <t>26华能水电SCP012</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10368,60 +10460,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>232680047.IB</t>
+          <t>012682478.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>10+5</t>
+          <t>0.47Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>50.0</v>
+        <v>14.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>50.0</v>
+        <v>14.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.25</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.36 ~ 1.48</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>20.48</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>25建行二级资本债02B(BC)</t>
+          <t>26华能水电SCP008</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>8.76Y+5.00Y</t>
+          <t>179D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.4756</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.8825/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司</t>
+          <t>华能澜沧江水电股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>S- 85.97</t>
+          <t>C 25.67</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10441,19 +10537,23 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>2.6571</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10461,35 +10561,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行所募集的资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
+          <t>本期超短期融资券募集资金14亿元,募集资金拟用于偿还金融机构借款4亿元和偿还26华能水电SCP006的本金10亿元[26华能水电SCP006]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,交通银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,平安银行股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司,中银国际证券股份有限公司,国信证券股份有限公司,国开证券股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10499,7 +10595,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司2026年二级资本债券(第三期)(债券通)(品种二)</t>
+          <t>华能澜沧江水电股份有限公司2026年度第十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10509,60 +10605,60 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2041-10-21</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>水电</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AO45" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ45" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR45" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>国有银行</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>2036-10-21</t>
-        </is>
-      </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10570,12 +10666,12 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY45" s="3" t="inlineStr">
@@ -10588,7 +10684,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26丽水城投MTN001</t>
+          <t>26建行二级资本债03B(BC)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10598,60 +10694,60 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102684088.IB</t>
+          <t>232680047.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10+5</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>7.3</v>
+        <v>50.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>7.3</v>
+        <v>50.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.65 ~ 2.25</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>25丽水城投MTN001</t>
+          <t>25建行二级资本债02B(BC)</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.99Y+2.00Y</t>
+          <t>8.76Y+5.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6090</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8825/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>丽水市城市建设投资集团有限公司</t>
+          <t>中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 11.64</t>
+          <t>S- 85.97</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10661,12 +10757,12 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -10674,52 +10770,52 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U46" s="4" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z46" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额为7.30亿元,拟用于偿还非金融企业债务融资工具本金[23丽水城投PPN001]</t>
+          <t>本期债券发行所募集的资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,交通银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,平安银行股份有限公司,中信建投证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司,中银国际证券股份有限公司,国信证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10729,7 +10825,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>丽水市城市建设投资集团有限公司2026年度第一期中期票据</t>
+          <t>中国建设银行股份有限公司2026年二级资本债券(第三期)(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10739,18 +10835,18 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-10-21</t>
+          <t>2041-10-21</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t/>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
@@ -10760,37 +10856,37 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2036-10-21</t>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
@@ -10800,12 +10896,12 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY46" s="3" t="inlineStr">
@@ -10818,7 +10914,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26乐清湾MTN002</t>
+          <t>26丽水城投MTN001</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10828,45 +10924,49 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>102684085.IB</t>
+          <t>102684088.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.0</v>
+        <v>7.3</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1.0</v>
+        <v>7.3</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>33.3</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26乐清湾MTN001</t>
+          <t>25丽水城投MTN001</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.29Y</t>
+          <t>1.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7946</t>
+          <t>1.6090</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10876,12 +10976,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>浙江乐清湾铁路有限公司</t>
+          <t>丽水市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 11.64</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10891,52 +10991,54 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U47" s="4" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="V47" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额10,000.00万元,募集资金用于偿还有息债务</t>
+          <t>发行人本期债务融资工具发行金额为7.30亿元,拟用于偿还非金融企业债务融资工具本金[23丽水城投PPN001]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10957,7 +11059,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>浙江乐清湾铁路有限公司2026年度第二期中期票据</t>
+          <t>丽水市城市建设投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10967,53 +11069,53 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-21</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM47" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP47" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -11046,55 +11148,59 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26江西长旅SCP001</t>
+          <t>26乐清湾MTN002</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>10-20 18:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>012682472.IB</t>
+          <t>102684085.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+          <t>1.60 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>52.26</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>18首旅债01</t>
+          <t>26乐清湾MTN001</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>2.29Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.4936</t>
+          <t>1.7946</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -11104,10 +11210,14 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>江西省长天旅游集团有限公司</t>
-        </is>
-      </c>
-      <c r="P48" s="3"/>
+          <t>浙江乐清湾铁路有限公司</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -11120,47 +11230,53 @@
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="U48" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行规模6亿元,全部用于偿还到期有息债务</t>
+          <t>本次中期票据发行金额10,000.00万元,募集资金用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11175,7 +11291,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>江西省长天旅游集团有限公司2026年度第一期超短期融资券</t>
+          <t>浙江乐清湾铁路有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11185,17 +11301,17 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
+          <t>2029-10-20</t>
         </is>
       </c>
       <c r="AK48" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11205,33 +11321,33 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>消费者服务</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>医疗服务</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11256,82 +11372,76 @@
       </c>
       <c r="AY48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AZ48" s="4" t="n">
-        <v>0.0</v>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AZ48" s="3"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26中建五局SCP004</t>
+          <t>26江西长旅SCP001</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-20 18:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>012682473.IB</t>
+          <t>012682472.IB</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26中建五局MTN001</t>
+          <t>18首旅债01</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.44Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.4936</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/1.5700</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第五工程局有限公司</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>B 54.22</t>
-        </is>
-      </c>
+          <t>江西省长天旅游集团有限公司</t>
+        </is>
+      </c>
+      <c r="P49" s="3"/>
       <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -11344,28 +11454,22 @@
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="U49" s="4" t="n">
-        <v>1.47</v>
-      </c>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X49" s="3" t="inlineStr">
-        <is>
-          <t>1.42%~1.46%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X49" s="3"/>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11374,17 +11478,17 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行的10亿元超短期融资券募集资金扣除发行费用后,拟用于偿还发行人本部的到期债务</t>
+          <t>本次债券发行规模6亿元,全部用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>长沙银行股份有限公司,东莞银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
@@ -11395,7 +11499,7 @@
       </c>
       <c r="AF49" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG49" s="3" t="inlineStr">
@@ -11405,7 +11509,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第五工程局有限公司2026年度第四期超短期融资券</t>
+          <t>江西省长天旅游集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11415,90 +11519,88 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2027-07-18</t>
         </is>
       </c>
       <c r="AK49" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL49" s="3" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP49" s="3"/>
+      <c r="AQ49" s="3" t="inlineStr">
+        <is>
+          <t>消费者服务</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>综合消费者服务</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>综合消费者服务</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>医疗服务</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY49" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="AO49" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ49" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR49" s="3" t="inlineStr">
-        <is>
-          <t>房屋建筑</t>
-        </is>
-      </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>其他房建</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW49" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX49" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY49" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ49" s="3"/>
+      <c r="AZ49" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26鄂能源SCP009</t>
+          <t>26中建五局SCP004</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11508,60 +11610,64 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>012682479.IB</t>
+          <t>012682473.IB</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.6Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.48</t>
-        </is>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>15.94</v>
+      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26鄂能源SCP008</t>
+          <t>26中建五局MTN001</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>134D</t>
+          <t>2.44Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.4706</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>1.4750/--</t>
+          <t>--/1.5700</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>湖北能源集团股份有限公司</t>
+          <t>中国建筑第五工程局有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B- 41.75</t>
+          <t>B 54.22</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11576,7 +11682,7 @@
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
@@ -11585,19 +11691,17 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>1.04</v>
-      </c>
+        <v>1.47</v>
+      </c>
+      <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11608,17 +11712,17 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额8亿元,全部用于发行人及子公司日常经营周转及偿还有息债务本息。</t>
+          <t>发行人本期发行的10亿元超短期融资券募集资金扣除发行费用后,拟用于偿还发行人本部的到期债务</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+          <t>长沙银行股份有限公司,东莞银行股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
@@ -11639,7 +11743,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>湖北能源集团股份有限公司2026年度第九期超短期融资券</t>
+          <t>中国建筑第五工程局有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11649,10 +11753,14 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
-        </is>
-      </c>
-      <c r="AK50" s="3"/>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="AK50" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL50" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -11675,27 +11783,27 @@
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11728,7 +11836,7 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26榆林城投MTN001A</t>
+          <t>26鄂能源SCP009</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11738,60 +11846,64 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>102690078.IB</t>
+          <t>012682479.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.6Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>4.5</v>
+        <v>8.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4.5</v>
+        <v>8.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+          <t>1.35 ~ 1.48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>25.45</v>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>24榆林城投MTN001</t>
+          <t>26鄂能源SCP008</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>134D</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.6387</t>
+          <t>1.4706</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4750/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>榆林市城市投资经营集团有限公司</t>
+          <t>湖北能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 13.28</t>
+          <t>B- 41.75</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11801,7 +11913,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>10-19 14:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11814,16 +11926,20 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
+      <c r="U51" s="4" t="n">
+        <v>1.6375</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>1.04</v>
+      </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
@@ -11834,28 +11950,28 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>陕西省-榆林市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为9.00亿元,募集资金用于偿还到期的债务融资工具[21榆林城投MTN003]</t>
+          <t>本期超短期融资券发行金额8亿元,全部用于发行人及子公司日常经营周转及偿还有息债务本息。</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
@@ -11865,7 +11981,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>榆林市城市投资经营集团有限公司2026年度第一期中期票据(品种一)</t>
+          <t>湖北能源集团股份有限公司2026年度第九期超短期融资券</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11875,14 +11991,10 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK51" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-28</t>
+        </is>
+      </c>
+      <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -11900,32 +12012,32 @@
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11958,7 +12070,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26三明城投MTN003</t>
+          <t>26榆林城投MTN001A</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11968,45 +12080,49 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>102684099.IB</t>
+          <t>102690078.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>5.8</v>
+        <v>2.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>37.26</v>
+      </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26三明城投MTN002</t>
+          <t>24榆林城投MTN001</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.65Y+2.00Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7339</t>
+          <t>1.6387</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -12016,12 +12132,12 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>三明市城市建设投资集团有限公司</t>
+          <t>榆林市城市投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C- 16.07</t>
+          <t>C- 13.28</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12031,7 +12147,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 14:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12044,41 +12160,37 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U52" s="4" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>2.21</v>
-      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>福建省-三明市</t>
+          <t>陕西省-榆林市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行金额为人民币0亿元,发行金额上限为人民币5.8亿元,募集资金拟用于偿还发行人即将到期的债务融资工具。[23三明城投MTN001]</t>
+          <t>本期发行金额为9.00亿元,募集资金用于偿还到期的债务融资工具[21榆林城投MTN003]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,厦门银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
@@ -12099,7 +12211,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>三明市城市建设投资集团有限公司2026年度第三期中期票据</t>
+          <t>榆林市城市投资经营集团有限公司2026年度第一期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12134,32 +12246,32 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12174,7 +12286,7 @@
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr">
@@ -12187,62 +12299,64 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ52" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ52" s="3"/>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26蚌埠城投MTN003</t>
+          <t>26三明城投MTN003</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>10-20 18:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102684106.IB</t>
+          <t>102684099.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>10.0</v>
+        <v>5.8</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.0</v>
+        <v>5.8</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>50.26</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26蚌埠城投MTN002</t>
+          <t>26三明城投MTN002</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.72Y</t>
+          <t>2.65Y+2.00Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6661</t>
+          <t>1.7339</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12252,12 +12366,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>蚌埠市城市投资控股有限公司</t>
+          <t>三明市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 15.18</t>
+          <t>C- 16.07</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12267,7 +12381,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12277,40 +12391,44 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>2.21</v>
+      </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>安徽省-蚌埠市</t>
+          <t>福建省-三明市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,募集资金用途用于偿还到期有息债务[23蚌埠城投PPN004]</t>
+          <t>本期中期票据基础发行金额为人民币0亿元,发行金额上限为人民币5.8亿元,募集资金拟用于偿还发行人即将到期的债务融资工具。[23三明城投MTN001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,兴业银行股份有限公司</t>
+          <t>申万宏源证券有限公司,厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
@@ -12331,7 +12449,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>蚌埠市城市投资控股有限公司2026年度第三期中期票据</t>
+          <t>三明市城市建设投资集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12341,17 +12459,17 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2029-10-21</t>
+          <t>2029-10-20</t>
         </is>
       </c>
       <c r="AK53" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM53" s="3" t="inlineStr">
@@ -12361,7 +12479,7 @@
       </c>
       <c r="AN53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AO53" s="3" t="inlineStr">
@@ -12406,7 +12524,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12416,27 +12534,27 @@
       </c>
       <c r="AY53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AZ53" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26淄博城资MTN003A</t>
+          <t>26蚌埠城投MTN003</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-20 18:00</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102684100.IB</t>
+          <t>102684106.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -12445,51 +12563,51 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26淄博城资MTN002A</t>
+          <t>26蚌埠城投MTN002</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>2.72Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7242</t>
+          <t>1.6661</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6900</t>
+          <t>1.6700/1.6400</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司</t>
+          <t>蚌埠市城市投资控股有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>B- 42.88</t>
+          <t>C- 15.18</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12509,40 +12627,40 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>安徽省-蚌埠市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据募集资金用途拟全部用于本级偿还债务融资工具本金。[21淄博城运MTN003]</t>
+          <t>本期中期票据发行规模10亿元,募集资金用途用于偿还到期有息债务[23蚌埠城投PPN004]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,平安银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12563,7 +12681,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司2026年度第三期中期票据(品种一)</t>
+          <t>蚌埠市城市投资控股有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12573,90 +12691,92 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
+          <t>2029-10-21</t>
         </is>
       </c>
       <c r="AK54" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL54" s="3" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM54" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN54" s="3" t="inlineStr">
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY54" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="AO54" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ54" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR54" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS54" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV54" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW54" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX54" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY54" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ54" s="3"/>
+      <c r="AZ54" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26榆林城投MTN001B</t>
+          <t>26淄博城资MTN003A</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12666,23 +12786,23 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102690079.IB</t>
+          <t>102684100.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.5</v>
+        <v>5.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4.5</v>
+        <v>5.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H55" s="3"/>
@@ -12694,32 +12814,32 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>24榆林城投MTN002</t>
+          <t>26淄博城资MTN002A</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>3.08Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.6438</t>
+          <t>1.7242</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.5900</t>
+          <t>1.7100/1.6900</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>榆林市城市投资经营集团有限公司</t>
+          <t>淄博市城市资产运营集团有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 13.28</t>
+          <t>B- 42.88</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12729,7 +12849,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>10-19 14:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12746,12 +12866,12 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -12762,17 +12882,17 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>陕西省-榆林市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为9.00亿元,募集资金用于偿还到期的债务融资工具[21榆林城投MTN003]</t>
+          <t>发行人本期中期票据募集资金用途拟全部用于本级偿还债务融资工具本金。[21淄博城运MTN003]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -12793,7 +12913,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>榆林市城市投资经营集团有限公司2026年度第一期中期票据(品种二)</t>
+          <t>淄博市城市资产运营集团有限公司2026年度第三期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12803,10 +12923,14 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK55" s="3"/>
+          <t>2029-10-20</t>
+        </is>
+      </c>
+      <c r="AK55" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL55" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -12824,12 +12948,12 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
@@ -12849,7 +12973,7 @@
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -12882,7 +13006,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26浙国贸SCP005</t>
+          <t>26榆林城投MTN001B</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12892,58 +13016,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>012682480.IB</t>
+          <t>102690079.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>37.3</v>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>24浙国贸MTN001</t>
+          <t>24榆林城投MTN002</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>154D</t>
+          <t>3.08Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.4919</t>
+          <t>1.6438</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.4900/--</t>
+          <t>1.6600/1.5900</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>浙江省国际贸易集团有限公司</t>
+          <t>榆林市城市投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C 27.57</t>
+          <t>C- 13.28</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -12953,12 +13083,12 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 14:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
@@ -12967,17 +13097,15 @@
         </is>
       </c>
       <c r="U56" s="3"/>
-      <c r="V56" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -12988,23 +13116,23 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>陕西省-榆林市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4亿元，募集资金拟用于偿还发行人即将到期的债务融资工具本金[26浙国贸SCP001]</t>
+          <t>本期发行金额为9.00亿元,募集资金用于偿还到期的债务融资工具[21榆林城投MTN003]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
@@ -13019,7 +13147,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>浙江省国际贸易集团有限公司2026年度第五期超短期融资券</t>
+          <t>榆林市城市投资经营集团有限公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13029,7 +13157,7 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
+          <t>2031-10-20</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -13050,12 +13178,12 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
@@ -13065,17 +13193,17 @@
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13108,7 +13236,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP001</t>
+          <t>26浙国贸SCP005</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13118,7 +13246,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>012682474.IB</t>
+          <t>012682480.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -13127,9 +13255,11 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
@@ -13139,37 +13269,37 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>24闽高速MTN001</t>
+          <t>24浙国贸MTN001</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>326D</t>
+          <t>154D</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.4933</t>
+          <t>1.4919</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>1.4900/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司</t>
+          <t>浙江省国际贸易集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C+ 35.00</t>
+          <t>C 27.57</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13184,7 +13314,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
@@ -13193,19 +13323,19 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>4.24</v>
+        <v>3.2</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>1.45</v>
+        <v>1.0</v>
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -13216,17 +13346,17 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模为人民币8亿元，用于偿还发行人到期债务</t>
+          <t>本期超短期融资券发行金额4亿元，募集资金拟用于偿还发行人即将到期的债务融资工具本金[26浙国贸SCP001]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行</t>
+          <t>杭州银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
@@ -13247,7 +13377,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司2026年度第一期超短期融资券</t>
+          <t>浙江省国际贸易集团有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13257,14 +13387,10 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
-        </is>
-      </c>
-      <c r="AK57" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -13282,7 +13408,7 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
@@ -13292,22 +13418,22 @@
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13340,7 +13466,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26巨化MTN003(科创债)</t>
+          <t>26闽高速SCP001</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13350,60 +13476,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>102684090.IB</t>
+          <t>012682474.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>23.84</v>
+      </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26巨化MTN002(科创债)</t>
+          <t>24闽高速MTN001</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>326D</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.6528</t>
+          <t>1.4933</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>巨化集团有限公司</t>
+          <t>福建省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C- 21.62</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13418,7 +13548,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -13427,17 +13557,19 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V58" s="3"/>
+        <v>4.24</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>1.45</v>
+      </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13448,23 +13580,23 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模5亿元,用于偿还发行人存量有息负债[23巨化03]</t>
+          <t>发行人本期超短期融资券发行规模为人民币8亿元，用于偿还发行人到期债务</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>国家开发银行</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13479,7 +13611,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>巨化集团有限公司2026年度第三期科技创新债券</t>
+          <t>福建省高速公路集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13489,10 +13621,14 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK58" s="3"/>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="AK58" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL58" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -13510,32 +13646,32 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13568,7 +13704,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26甬交投集SCP004</t>
+          <t>26巨化MTN003(科创债)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13578,58 +13714,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>012682484.IB</t>
+          <t>102684090.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>34.3</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26甬交投集SCP002</t>
+          <t>26巨化MTN002(科创债)</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>174D</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.4727</t>
+          <t>1.6528</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>宁波交通投资集团有限公司</t>
+          <t>巨化集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 13.94</t>
+          <t>C- 21.62</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13644,7 +13786,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -13653,19 +13795,17 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>3.19</v>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13676,23 +13816,23 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行超短期融资券160,000.00万元,用于归还发行人的存量债券本金[26甬交投集SCP001]</t>
+          <t>本期债务融资工具发行规模5亿元,用于偿还发行人存量有息负债[23巨化03]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>宁波银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -13707,7 +13847,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>宁波交通投资集团有限公司2026年度第四期超短期融资券</t>
+          <t>巨化集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13717,14 +13857,10 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
-        </is>
-      </c>
-      <c r="AK59" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-20</t>
+        </is>
+      </c>
+      <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -13742,32 +13878,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13795,14 +13931,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26大横琴MTN002</t>
+          <t>26甬交投集SCP004</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13812,58 +13946,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>102684094.IB</t>
+          <t>012682484.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>16.0</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>16.0</v>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+          <t>1.40 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>33.84</v>
+      </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26大横琴MTN001</t>
+          <t>26甬交投集SCP002</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.85Y+N</t>
+          <t>174D</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.7708</t>
+          <t>1.4727</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司</t>
+          <t>宁波交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>B- 43.19</t>
+          <t>C- 13.94</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13878,7 +14018,7 @@
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -13886,18 +14026,20 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U60" s="3"/>
+      <c r="U60" s="4" t="n">
+        <v>3.67</v>
+      </c>
       <c r="V60" s="4" t="n">
-        <v>1.5</v>
+        <v>3.19</v>
       </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -13908,23 +14050,23 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行拟募集资金8.00亿元,全部用于偿还本部到期债务融资工具本金[21大横琴MTN002(绿色)]</t>
+          <t>发行人本期拟发行超短期融资券160,000.00万元,用于归还发行人的存量债券本金[26甬交投集SCP001]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
@@ -13939,7 +14081,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>珠海大横琴集团有限公司2026年度第二期中期票据</t>
+          <t>宁波交通投资集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -13949,7 +14091,7 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
+          <t>2027-07-17</t>
         </is>
       </c>
       <c r="AK60" s="3" t="inlineStr">
@@ -13979,7 +14121,7 @@
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
@@ -13989,17 +14131,17 @@
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14014,7 +14156,7 @@
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -14027,12 +14169,14 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ60" s="3"/>
+      <c r="AZ60" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26淄博城资MTN003B</t>
+          <t>26大横琴MTN002</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14042,60 +14186,64 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102684101.IB</t>
+          <t>102684094.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>50.26</v>
+      </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26淄博城资MTN002B</t>
+          <t>26大横琴MTN001</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.85Y+N</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.8376</t>
+          <t>1.7708</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司</t>
+          <t>珠海大横琴集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>B- 42.88</t>
+          <t>B- 43.19</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14110,7 +14258,7 @@
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
@@ -14119,15 +14267,17 @@
         </is>
       </c>
       <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
+      <c r="V61" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14138,17 +14288,17 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据募集资金用途拟全部用于本级偿还债务融资工具本金。[21淄博城运MTN003]</t>
+          <t>发行人本期中期票据发行拟募集资金8.00亿元,全部用于偿还本部到期债务融资工具本金[21大横琴MTN002(绿色)]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,平安银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -14169,7 +14319,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>珠海大横琴集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14179,10 +14329,14 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK61" s="3"/>
+          <t>2029-10-20</t>
+        </is>
+      </c>
+      <c r="AK61" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -14200,7 +14354,7 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
@@ -14210,17 +14364,17 @@
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
@@ -14240,7 +14394,7 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
@@ -14258,7 +14412,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN020</t>
+          <t>26淄博城资MTN003B</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14268,7 +14422,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102684089.IB</t>
+          <t>102684101.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -14277,26 +14431,30 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.78</t>
-        </is>
-      </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+          <t>1.60 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>42.3</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN017</t>
+          <t>26淄博城资MTN002B</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -14306,22 +14464,22 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.8142</t>
+          <t>1.8376</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>淄博市城市资产运营集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.55</t>
+          <t>B- 42.88</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14344,16 +14502,20 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
+      <c r="U62" s="4" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>1.15</v>
+      </c>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -14364,17 +14526,17 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债</t>
+          <t>发行人本期中期票据募集资金用途拟全部用于本级偿还债务融资工具本金。[21淄博城运MTN003]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,广发银行股份有限公司</t>
+          <t>兴业银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14395,7 +14557,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第二十期中期票据</t>
+          <t>淄博市城市资产运营集团有限公司2026年度第三期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14436,22 +14598,22 @@
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14479,14 +14641,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ62" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ62" s="3"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP030</t>
+          <t>26晋能煤业MTN020</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14496,60 +14656,64 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>012682481.IB</t>
+          <t>102684089.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>0.2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.46</t>
-        </is>
-      </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+          <t>1.50 ~ 1.78</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>40.3</v>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP028</t>
+          <t>26晋能煤业MTN017</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>61D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.4425</t>
+          <t>1.8142</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>A- 61.64</t>
+          <t>C+ 33.55</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14559,7 +14723,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>10-19 11:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -14576,39 +14740,39 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后拟全部用于偿还发行人本部即将到期的债务融资工具本金。[26夏商SCP021]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>平安银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
@@ -14623,7 +14787,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第三十期超短期融资券</t>
+          <t>晋能控股煤业集团有限公司2026年度第二十期中期票据</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14633,7 +14797,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2031-10-20</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14659,27 +14823,27 @@
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -14714,7 +14878,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26国能资本MTN002</t>
+          <t>26夏商SCP030</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14724,60 +14888,60 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>102684104.IB</t>
+          <t>012682481.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.2Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.62</t>
+          <t>1.30 ~ 1.46</t>
         </is>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26国能资本MTN001</t>
+          <t>26夏商SCP028</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>1.67Y</t>
+          <t>61D</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.5470</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.5700/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团资本控股有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>B- 49.62</t>
+          <t>A- 61.64</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14787,12 +14951,12 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 11:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr">
@@ -14800,52 +14964,48 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U64" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.65%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元，拟全部用于偿还子公司的有息负债</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后拟全部用于偿还发行人本部即将到期的债务融资工具本金。[26夏商SCP021]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商证券股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -14855,7 +15015,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团资本控股有限公司2026年度第二期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第三十期超短期融资券</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -14865,14 +15025,10 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK64" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -14890,32 +15046,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -14943,12 +15099,14 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ64" s="3"/>
+      <c r="AZ64" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP004</t>
+          <t>26国能资本MTN002</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -14958,58 +15116,64 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>012682476.IB</t>
+          <t>102684104.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
-        </is>
-      </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+          <t>1.40 ~ 1.62</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>31.26</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP002</t>
+          <t>26国能资本MTN001</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>228D</t>
+          <t>1.67Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.5081</t>
+          <t>1.5470</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.5700/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>国家能源集团资本控股有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>B- 36.67</t>
+          <t>B- 49.62</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15024,7 +15188,7 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
@@ -15033,19 +15197,19 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="V65" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.37%~1.41%</t>
+          <t>1.55%~1.65%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15061,18 +15225,18 @@
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
+          <t>本期中期票据发行规模10亿元，拟全部用于偿还子公司的有息负债</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15087,7 +15251,7 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第四期超短期融资券</t>
+          <t>国家能源集团资本控股有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -15097,10 +15261,14 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-      <c r="AK65" s="3"/>
+          <t>2029-10-20</t>
+        </is>
+      </c>
+      <c r="AK65" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL65" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -15118,32 +15286,32 @@
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15176,7 +15344,7 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26华能水电SCP012</t>
+          <t>26中兵物资SCP004</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15186,25 +15354,31 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>012682478.IB</t>
+          <t>012682476.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>0.47Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.36 ~ 1.48</t>
-        </is>
-      </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+          <t>1.35 ~ 1.55</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>23.84</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -15212,32 +15386,32 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>26华能水电SCP008</t>
+          <t>26中兵物资SCP002</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>179D</t>
+          <t>228D</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.4756</t>
+          <t>1.5081</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C 25.67</t>
+          <t>B- 36.67</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15252,7 +15426,7 @@
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
@@ -15261,19 +15435,19 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>1.1</v>
+        <v>1.0</v>
       </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.37%~1.41%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -15284,17 +15458,17 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金14亿元,募集资金拟用于偿还金融机构借款4亿元和偿还26华能水电SCP006的本金10亿元[26华能水电SCP006]</t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -15315,7 +15489,7 @@
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司2026年度第十二期超短期融资券</t>
+          <t>中国兵工物资集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15325,7 +15499,7 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2027-07-16</t>
         </is>
       </c>
       <c r="AK66" s="3"/>
@@ -15351,27 +15525,27 @@
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
@@ -15425,14 +15599,20 @@
       <c r="E67" s="4" t="n">
         <v>12.0</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="4" t="n">
+        <v>12.0</v>
+      </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1.65 ~ 1.90</t>
         </is>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>51.84</v>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -15893,8 +16073,12 @@
           <t>2.50 ~ 3.50</t>
         </is>
       </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+      <c r="H69" s="4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>150.26</v>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
           <t>2.85</t>
@@ -16121,8 +16305,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="H70" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>48.78</v>
+      </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -16345,8 +16533,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="H71" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>47.78</v>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -16577,8 +16769,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="H72" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>15.26</v>
+      </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -17310,7 +17506,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U75" s="3"/>
+      <c r="U75" s="4" t="n">
+        <v>5.3</v>
+      </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
@@ -17762,7 +17960,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U77" s="3"/>
+      <c r="U77" s="4" t="n">
+        <v>3.43</v>
+      </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
@@ -18222,7 +18422,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U79" s="3"/>
+      <c r="U79" s="4" t="n">
+        <v>3.87</v>
+      </c>
       <c r="V79" s="3"/>
       <c r="W79" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-10-19.xlsx
+++ b/data/credit_bond_all_2026-10-19.xlsx
@@ -6796,59 +6796,59 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26江西长旅SCP001</t>
+          <t>26商丘01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-20 18:00</t>
+          <t>10-19 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>012682472.IB</t>
+          <t>284149.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.0</v>
+        <v>7.24</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.0</v>
+        <v>7.24</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>43.19</v>
+        <v>60.3</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>18首旅债01</t>
+          <t>25商丘06</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>304D</t>
+          <t>4.06Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.4936</t>
+          <t>1.9639</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6858,12 +6858,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>江西省长天旅游集团有限公司</t>
+          <t>商丘市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 35.91</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6873,60 +6873,58 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>4.0815</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.82%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>河南省-商丘市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行规模6亿元,全部用于偿还到期有息债务</t>
+          <t>本期债券募集资金不超过(含)7.24亿元,扣除发行费用后,拟全部用于偿还前次公司债券本金[26商丘D1,21商资03]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
+          <t>平安证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,中信建投证券股份有限公司,中泰证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6936,68 +6934,68 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>江西省长天旅游集团有限公司2026年度第一期超短期融资券</t>
+          <t>商丘市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-07-18</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-20</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP29" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>消费者服务</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>医疗服务</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7022,17 +7020,15 @@
       </c>
       <c r="AY29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AZ29" s="4" t="n">
-        <v>0.0</v>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AZ29" s="3"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>K26青矩1</t>
+          <t>26鲁高05</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7042,106 +7038,118 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>821032.BJ</t>
+          <t>246284.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3</v>
+        <v>30.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.2</v>
+        <v>30.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.00 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>50.87</v>
+        <v>32.03</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>26鲁高02</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>9.76Y</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1.9308</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>山东高速集团有限公司</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>B- 43.26</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>10-19 16:00</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>青矩技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>10-19 15:00</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.0</v>
+        <v>2.3633</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过0.30亿元,本期公司债券募集资金扣除发行费用后,拟全部用于补充营运资金</t>
+          <t>本期债券拟募集资金30亿元,扣除发行费用后拟用于偿还到期有息债务及其他有息负债。[23鲁高速MTN009]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD30" s="3" t="inlineStr">
-        <is>
-          <t>北京中关村科技融资担保有限公司</t>
-        </is>
-      </c>
+          <t>申万宏源证券有限公司,中泰证券股份有限公司,东方证券股份有限公司,东兴证券股份有限公司,德邦证券股份有限公司,华福证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7149,17 +7157,17 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>北交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>青矩技术股份有限公司2026年面向专业投资者公开发行科技创新公司债券(专精特新)(第一期)</t>
+          <t>山东高速集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7169,59 +7177,63 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-10-22</t>
+          <t>2036-10-20</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP30" s="3"/>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>专业服务</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>咨询服务</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>咨询服务</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr">
@@ -7244,53 +7256,59 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26鲤水05(取消发行)</t>
+          <t>26厦钨SCP003</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>10-19 19:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>DY284252.SH</t>
+          <t>012682483.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>27.84</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24鲤水01</t>
+          <t>26厦钨SCP002</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>225D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6844</t>
+          <t>1.5073</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7300,12 +7318,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>泉州水务集团有限公司</t>
+          <t>厦门钨业股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 13.32</t>
+          <t>B- 41.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7315,56 +7333,60 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.13</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期有息债务</t>
+          <t>本期超短期融资券发行金额5亿元,拟全部用于偿还发行人本部银行贷款(提前还款)</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7374,32 +7396,32 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>泉州水务集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)(取消发行)</t>
+          <t>厦门钨业股份有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-10-21</t>
+          <t>2027-07-17</t>
         </is>
       </c>
       <c r="AK31" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7409,37 +7431,37 @@
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>稀有稀土金属</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7472,74 +7494,74 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26鲤水06</t>
+          <t>26江西长旅SCP001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10-19 19:00</t>
+          <t>10-20 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>284253.SH</t>
+          <t>012682472.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.5</v>
+        <v>6.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>37.3</v>
+        <v>43.19</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26鲤水04</t>
+          <t>18首旅债01</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>304D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8490</t>
+          <t>1.4936</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.8600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>泉州水务集团有限公司</t>
+          <t>江西省长天旅游集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 13.32</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7549,12 +7571,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7563,44 +7585,46 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>2.35</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.78%~1.82%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期有息债务</t>
+          <t>本次债券发行规模6亿元,全部用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7610,75 +7634,75 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>泉州水务集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
+          <t>江西省长天旅游集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-10-21</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2027-07-18</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>消费者服务</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>综合消费者服务</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>综合消费者服务</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>医疗服务</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>水务</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7696,84 +7720,74 @@
       </c>
       <c r="AY32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ32" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26济南金投PPN001</t>
+          <t>K26青矩1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-19 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>032680577.IB</t>
+          <t>821032.BJ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.0</v>
+        <v>0.3</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.0</v>
+        <v>0.2</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>52.3</v>
+        <v>50.87</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>26济金Z1</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>2.47Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7261</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>济南金投控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>B- 36.13</t>
-        </is>
-      </c>
+          <t>青矩技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -7781,129 +7795,121 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>10-19 14:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.32</v>
+        <v>1.0</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t>1.86%~1.96%</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行金额为人民币0.00亿元,发行金额上限为人民币5.00亿元。其中3.00亿元用于偿还存续债务融资工具本息,2.00亿元用于融资租赁投放等符合相关法律法规要求的用途。</t>
+          <t>本期债券发行金额为不超过0.30亿元,本期公司债券募集资金扣除发行费用后,拟全部用于补充营运资金</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中信证券股份有限公司,中国光大银行股份有限公司,招商银行股份有限公司,上海浦东发展银行股份有限公司,青岛银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>北京中关村科技融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>北交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>济南金投控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>青矩技术股份有限公司2026年面向专业投资者公开发行科技创新公司债券(专精特新)(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
+          <t>2027-10-22</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>专业服务</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7913,7 +7919,7 @@
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
@@ -7936,17 +7942,17 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26宏河控股PPN002</t>
+          <t>26鲤水05(取消发行)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-19 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>032680580.IB</t>
+          <t>DY284252.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7955,40 +7961,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.50</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>150.26</v>
-      </c>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26宏河控股PPN001(并购)</t>
+          <t>24鲤水01</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.89Y+2.00Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.8304</t>
+          <t>1.6844</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>山东宏河控股集团有限公司</t>
+          <t>泉州水务集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C 26.79</t>
+          <t>C- 13.32</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8013,58 +8013,56 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>1.45</v>
-      </c>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.74%~2.84%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模0亿元,发行规模上限2亿元。全部用于偿还有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司</t>
+          <t>兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8074,12 +8072,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>山东宏河控股集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>泉州水务集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8089,57 +8087,57 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
+          <t>2029-10-21</t>
         </is>
       </c>
       <c r="AK34" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8167,81 +8165,79 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ34" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ34" s="3"/>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP007</t>
+          <t>26鲤水06</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-19 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682475.IB</t>
+          <t>284253.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.24 ~ 1.44</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>26.94</v>
+        <v>37.3</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP003</t>
+          <t>26鲤水04</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>60D</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4211</t>
+          <t>1.8490</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8600/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司</t>
+          <t>泉州水务集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 20.51</t>
+          <t>C- 13.32</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8251,7 +8247,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8261,119 +8257,119 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.4</v>
+        <v>3.87</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期有息债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司</t>
+          <t>兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司2026年度第七期超短期融资券</t>
+          <t>泉州水务集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2031-10-21</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8401,14 +8397,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26闽高速SCP001</t>
+          <t>26济南金投PPN001</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8418,64 +8412,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>012682474.IB</t>
+          <t>032680577.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23.84</v>
+        <v>52.3</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24闽高速MTN001</t>
+          <t>26济金Z1</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>326D</t>
+          <t>2.47Y+2.00Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.4933</t>
+          <t>1.7261</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>1.7100/1.7000</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司</t>
+          <t>济南金投控股集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 35.00</t>
+          <t>B- 36.13</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8485,12 +8479,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8499,46 +8493,44 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>4.2375</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>2.32</v>
+      </c>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模为人民币8亿元，用于偿还发行人到期债务</t>
+          <t>本期定向债务融资工具基础发行金额为人民币0.00亿元,发行金额上限为人民币5.00亿元。其中3.00亿元用于偿还存续债务融资工具本息,2.00亿元用于融资租赁投放等符合相关法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行</t>
+          <t>光大证券股份有限公司,中信证券股份有限公司,中国光大银行股份有限公司,招商银行股份有限公司,上海浦东发展银行股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8553,24 +8545,20 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>福建省高速公路集团有限公司2026年度第一期超短期融资券</t>
+          <t>济南金投控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-20</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -8588,32 +8576,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8646,59 +8634,59 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26赣金Y1</t>
+          <t>26宏河控股PPN002</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>10-19 19:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>525046.SZ</t>
+          <t>032680580.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.98</t>
+          <t>2.50 ~ 3.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>47.78</v>
+        <v>150.26</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25赣金Y1</t>
+          <t>26宏河控股PPN001(并购)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>339D+N</t>
+          <t>2.89Y+2.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7238</t>
+          <t>2.8304</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8708,12 +8696,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>江西省金融资产管理股份有限公司</t>
+          <t>山东宏河控股集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 15.64</t>
+          <t>C 26.79</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8723,12 +8711,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8737,44 +8725,44 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.74%~2.84%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债券本金,剩余部分用于补充公司流动资金。[24赣金Y1]</t>
+          <t>本次定向债务融资工具基础发行规模0亿元,发行规模上限2亿元。全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,兴业证券股份有限公司</t>
+          <t>青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8784,168 +8772,174 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>江西省金融资产管理股份有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
+          <t>山东宏河控股集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2028-10-20</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2029-10-20</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY37" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW37" s="3" t="inlineStr">
-        <is>
-          <t>永续</t>
-        </is>
-      </c>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>次级债权</t>
-        </is>
-      </c>
-      <c r="AY37" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26鲁高05</t>
+          <t>26中交投SCP007</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-19 19:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246284.SH</t>
+          <t>012682475.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.24 ~ 1.44</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32.03</v>
+        <v>26.94</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26鲁高02</t>
+          <t>26中交投SCP003</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>9.76Y</t>
+          <t>60D</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.9308</t>
+          <t>1.4211</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.9800/1.9300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>中交投资有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 43.26</t>
+          <t>C- 20.51</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8955,7 +8949,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-19 16:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8969,15 +8963,19 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>2.3633</v>
+        <v>0.4</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.43%~1.47%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8986,38 +8984,38 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金30亿元,扣除发行费用后拟用于偿还到期有息债务及其他有息负债。[23鲁高速MTN009]</t>
+          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,中泰证券股份有限公司,东方证券股份有限公司,东兴证券股份有限公司,德邦证券股份有限公司,华福证券股份有限公司</t>
+          <t>广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>中交投资有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9027,101 +9025,103 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2036-10-20</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>其他专业工程</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY38" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW38" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX38" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ38" s="3"/>
+      <c r="AZ38" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26微山02</t>
+          <t>26闽高速SCP001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>10-19 19:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>284298.SH</t>
+          <t>012682474.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -9132,48 +9132,48 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>82.3</v>
+        <v>23.84</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26微山01</t>
+          <t>24闽高速MTN001</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.24Y</t>
+          <t>326D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.2273</t>
+          <t>1.4933</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>微山县创达投资建设集团有限公司</t>
+          <t>福建省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 16.74</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>10-19 15:00</t>
+          <t>10-19 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9197,44 +9197,46 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>4.2375</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金规模不超过8.00亿元(含8.00亿元),债券募集资金扣除发行费用后拟全部用于偿还到期的公司债券本金。[23微山02]</t>
+          <t>发行人本期超短期融资券发行规模为人民币8亿元，用于偿还发行人到期债务</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>德邦证券股份有限公司</t>
+          <t>国家开发银行</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9244,28 +9246,32 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>微山县创达投资建设集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>福建省高速公路集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9285,27 +9291,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9338,7 +9344,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26商丘01</t>
+          <t>26赣金Y1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9348,64 +9354,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>284149.SH</t>
+          <t>525046.SZ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>7.24</v>
+        <v>7.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>7.24</v>
+        <v>7.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 1.98</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>60.3</v>
+        <v>47.78</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25商丘06</t>
+          <t>25赣金Y1</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.06Y</t>
+          <t>339D+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.9639</t>
+          <t>1.7238</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.9800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>商丘市发展投资集团有限公司</t>
+          <t>江西省金融资产管理股份有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 35.91</t>
+          <t>C- 15.64</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9429,7 +9435,7 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.0815</v>
+        <v>2.5</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
@@ -9439,7 +9445,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9450,17 +9456,17 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>河南省-商丘市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过(含)7.24亿元,扣除发行费用后,拟全部用于偿还前次公司债券本金[26商丘D1,21商资03]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债券本金,剩余部分用于补充公司流动资金。[24赣金Y1]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,华泰联合证券有限责任公司,第一创业证券承销保荐有限责任公司,中信建投证券股份有限公司,中泰证券股份有限公司,财通证券股份有限公司</t>
+          <t>国金证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9476,33 +9482,33 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>商丘市发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江西省金融资产管理股份有限公司2026年面向专业投资者公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
+          <t>2028-10-20</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t/>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9512,32 +9518,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9552,12 +9558,12 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY40" s="3" t="inlineStr">
@@ -9570,7 +9576,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26金禹01</t>
+          <t>26微山02</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9580,49 +9586,49 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>284292.SH</t>
+          <t>284298.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2.5</v>
+        <v>8.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2.5</v>
+        <v>8.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>49.78</v>
+        <v>82.3</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>24金禹01</t>
+          <t>26微山01</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>4.24Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.7764</t>
+          <t>2.2273</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9632,12 +9638,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>常德市金禹能源集团有限公司</t>
+          <t>微山县创达投资建设集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.83</t>
+          <t>C- 16.74</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9661,17 +9667,17 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9682,17 +9688,17 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,将用于置换已兑付公司债券本金的自有资金[23金禹01]</t>
+          <t>本期债券的募集资金规模不超过8.00亿元(含8.00亿元),债券募集资金扣除发行费用后拟全部用于偿还到期的公司债券本金。[23微山02]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9713,7 +9719,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>常德市金禹能源集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>微山县创达投资建设集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9723,13 +9729,13 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2028-10-20</t>
+          <t>2031-10-20</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9744,7 +9750,7 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
@@ -9754,17 +9760,17 @@
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
@@ -9802,70 +9808,74 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26浙商银行债01</t>
+          <t>26金禹01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>10-19 17:00</t>
+          <t>10-19 19:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>212680066.IB</t>
+          <t>284292.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>15.0</v>
+        <v>2.5</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="G42" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>30.26</v>
+        <v>49.78</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25浙商银行债01B</t>
+          <t>24金禹01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>3.33Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.5352</t>
+          <t>1.7764</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.5600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>常德市金禹能源集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>A 77.77</t>
+          <t>C+ 34.83</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9875,7 +9885,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:30</t>
+          <t>10-19 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9888,79 +9898,81 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4" t="n">
+        <v>2.24</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.62%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要、充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
-        </is>
-      </c>
-      <c r="AC42" s="3"/>
+          <t>本期公司债券募集资金扣除发行费用后,将用于置换已兑付公司债券本金的自有资金[23金禹01]</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司2026年金融债券(第一期)</t>
+          <t>常德市金禹能源集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-20</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9970,32 +9982,32 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -10028,74 +10040,70 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26华发集团SCP010</t>
+          <t>26浙商银行债01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-19 17:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>012682482.IB</t>
+          <t>212680066.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.07</t>
-        </is>
-      </c>
+        <v>25.0</v>
+      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="4" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>91.84</v>
+        <v>30.26</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>22华发集团MTN010(科创票据)</t>
+          <t>25浙商银行债01B</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>267D</t>
+          <t>3.33Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.0141</t>
+          <t>1.5352</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>B- 42.83</t>
+          <t>A 77.77</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10105,7 +10113,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>10-19 09:00</t>
+          <t>10-19 09:30</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10118,18 +10126,16 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U43" s="4" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.03%~2.07%</t>
+          <t>1.52%~1.62%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -10140,28 +10146,24 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,用于偿还发行人本部债务融资工具本金[26华发集团SCP003]</t>
-        </is>
-      </c>
-      <c r="AC43" s="3" t="inlineStr">
-        <is>
-          <t>上海银行股份有限公司,上海浦东发展银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要、充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
+        </is>
+      </c>
+      <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
@@ -10171,7 +10173,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年度第十期超短期融资券</t>
+          <t>浙商银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10181,7 +10183,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
+          <t>2029-10-20</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
@@ -10196,7 +10198,7 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
@@ -10206,32 +10208,32 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10259,14 +10261,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ43" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ43" s="3"/>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦CP010</t>
+          <t>26华发集团SCP010</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10276,64 +10276,64 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>042680346.IB</t>
+          <t>012682482.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.80 ~ 2.07</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18.94</v>
+        <v>91.84</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>22华发集团MTN010(科创票据)</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>267D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.4514</t>
+          <t>2.0141</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.4700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.89</t>
+          <t>B- 42.83</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -10357,19 +10357,17 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>2.03%~2.07%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10380,23 +10378,23 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行5亿元短期融资券，用于偿还发行人存量负债</t>
+          <t>本期超短期融资券发行规模为10亿元,用于偿还发行人本部债务融资工具本金[26华发集团SCP003]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,华夏银行股份有限公司</t>
+          <t>上海银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10411,7 +10409,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第十期短期融资券</t>
+          <t>珠海华发集团有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10421,10 +10419,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2027-07-17</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -10447,27 +10449,27 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10496,13 +10498,13 @@
         </is>
       </c>
       <c r="AZ44" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26河钢集GN001</t>
+          <t>26苏农垦CP010</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10512,64 +10514,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>132680103.IB</t>
+          <t>042680346.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.74</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>47.26</v>
+        <v>18.94</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>24河钢集MTN014</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.86Y+N</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7605</t>
+          <t>1.4514</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>河钢集团有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 28.40</t>
+          <t>C+ 33.89</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10584,7 +10586,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -10593,17 +10595,19 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V45" s="3"/>
+        <v>2.18</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10614,23 +10618,23 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为10亿元,本期债券募集资金拟全部用于置换近三月张宣高科高端装备核心零部件及关键材料制造项目及河钢集团石家庄钢铁有限责任公司环保搬迁产品升级改造项目废钢采购款。</t>
+          <t>发行人本次拟发行5亿元短期融资券，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
+          <t>南京银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10645,7 +10649,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>河钢集团有限公司2026年度第一期绿色中期票据</t>
+          <t>江苏省农垦集团有限公司2026年度第十期短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10655,14 +10659,10 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -10685,27 +10685,27 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10733,12 +10733,14 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业SCP012</t>
+          <t>26河钢集GN001</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10748,64 +10750,64 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682477.IB</t>
+          <t>132680103.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 1.90</t>
+          <t>1.50 ~ 1.74</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>51.84</v>
+        <v>47.26</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26华友钴业SCP010</t>
+          <t>24河钢集MTN014</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>214D</t>
+          <t>2.86Y+N</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6879</t>
+          <t>1.7605</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.7100/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司</t>
+          <t>河钢集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.02</t>
+          <t>C 28.40</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10820,7 +10822,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -10829,19 +10831,17 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>1.9083</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>2.83</v>
-      </c>
+        <v>1.18</v>
+      </c>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.81%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10852,28 +10852,28 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本次超短期融资券发行金额12亿元,其中10亿元用于偿还发行人本级债务融资工具本金、2亿元用于偿还发行人子公司银行借款。[26华友钴业SCP003]</t>
+          <t>本期中期票据发行规模为10亿元,本期债券募集资金拟全部用于置换近三月张宣高科高端装备核心零部件及关键材料制造项目及河钢集团石家庄钢铁有限责任公司环保搬迁产品升级改造项目废钢采购款。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国银行股份有限公司,渤海银行股份有限公司,招商银行股份有限公司,上海浦东发展银行股份有限公司,广发银行股份有限公司,上海农村商业银行股份有限公司,平安银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>浙江华友钴业股份有限公司2026年度第十二期超短期融资券</t>
+          <t>河钢集团有限公司2026年度第一期绿色中期票据</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10893,10 +10893,14 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2029-10-20</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -10919,7 +10923,7 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -10929,17 +10933,17 @@
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10954,7 +10958,7 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10967,14 +10971,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ46" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ46" s="3"/>
     </row>
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26厦钨SCP003</t>
+          <t>26华友钴业SCP012</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10984,7 +10986,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>012682483.IB</t>
+          <t>012682477.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10993,55 +10995,55 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.65 ~ 1.90</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>27.84</v>
+        <v>51.84</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26厦钨SCP002</t>
+          <t>26华友钴业SCP010</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>225D</t>
+          <t>214D</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5073</t>
+          <t>1.6879</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.5250/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>厦门钨业股份有限公司</t>
+          <t>浙江华友钴业股份有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>B- 41.00</t>
+          <t>C+ 33.02</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11056,7 +11058,7 @@
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -11065,19 +11067,19 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>3.76</v>
+        <v>1.9083</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>1.13</v>
+        <v>2.83</v>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.77%~1.81%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -11088,17 +11090,17 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,拟全部用于偿还发行人本部银行贷款(提前还款)</t>
+          <t>本次超短期融资券发行金额12亿元,其中10亿元用于偿还发行人本级债务融资工具本金、2亿元用于偿还发行人子公司银行借款。[26华友钴业SCP003]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国银行股份有限公司,渤海银行股份有限公司,招商银行股份有限公司,上海浦东发展银行股份有限公司,广发银行股份有限公司,上海农村商业银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -11109,7 +11111,7 @@
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
@@ -11119,7 +11121,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>厦门钨业股份有限公司2026年度第三期超短期融资券</t>
+          <t>浙江华友钴业股份有限公司2026年度第十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11129,14 +11131,10 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2027-07-17</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
@@ -11159,7 +11157,7 @@
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
@@ -11174,7 +11172,7 @@
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>稀有稀土金属</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
@@ -11207,7 +11205,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ47" s="3"/>
+      <c r="AZ47" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
